--- a/dataset_t6_grouped/results2/G4/G4_T3616_W0026F0002T0006Z000C1N31_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3616_W0026F0002T0006Z000C1N31_analysis.xlsx
@@ -480,10 +480,10 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>67.40592218232261</v>
+        <v>10.95346235462742</v>
       </c>
       <c r="D2" t="n">
-        <v>67.29299772670049</v>
+        <v>10.93511213058883</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
